--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
   <si>
     <t>Filename</t>
   </si>
@@ -808,706 +808,709 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9846,0.0014,0.0030,0.0016</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9963,0.0010,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.1131,0.0003,0.0000,0.9495</t>
+    <t>0.9634,0.0106,0.0021,0.0033</t>
+  </si>
+  <si>
+    <t>0.0006,0.0014,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0428,0.0002,0.0000,0.9865</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0024,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9917,0.0106,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0018,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0001,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0013,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0057,0.0012,0.9926,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0004,0.9983,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0058,0.9928,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9876,0.0001,0.0089,0.0001</t>
+  </si>
+  <si>
+    <t>0.0272,0.0018,0.9766,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.1993,0.0001,0.8847,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1093,0.9018,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.5827,0.4878,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,0.9999,0.0023</t>
+  </si>
+  <si>
+    <t>0.0075,0.9807,0.0142,0.0001</t>
+  </si>
+  <si>
+    <t>0.9930,0.0016,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9855,0.0039,0.0040,0.0008</t>
+  </si>
+  <si>
+    <t>0.7326,0.3178,0.0004,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0099,0.0000</t>
+  </si>
+  <si>
+    <t>0.0483,0.2612,0.1616,0.0085</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0323,0.9911,0.0001</t>
+  </si>
+  <si>
+    <t>0.2416,0.0000,0.3566,0.0022</t>
+  </si>
+  <si>
+    <t>0.0002,0.0481,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.6538,0.0088,0.9418</t>
+  </si>
+  <si>
+    <t>0.0004,0.9958,0.0009,0.0028</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.2346,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0048,0.9984,0.0004</t>
+  </si>
+  <si>
+    <t>0.0119,0.0044,0.9807,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0004,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0108,0.0006,0.9934,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0145,0.9923,0.0014</t>
+  </si>
+  <si>
+    <t>0.9974,0.0029,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9993,0.0005</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9972,0.9418,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0047,0.9983,0.0007</t>
+  </si>
+  <si>
+    <t>0.0052,0.0007,0.9923,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.9871,0.9905,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0130,0.9849,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9933,0.0003,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0007,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9952,0.9850,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9527,0.8434,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0062,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9929,0.9436,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0005,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0011,0.9999</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.4973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9601,0.7009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9717,0.0251,0.0058</t>
+  </si>
+  <si>
+    <t>0.0004,0.7425,0.9702,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9925,0.9661,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0067,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9928,0.0074,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9967,0.0026,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9981,0.0018,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9973,0.0035,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9971,0.0047,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9956,0.0055,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
+    <t>0.9991,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0031,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9986,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.9983,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.4461,0.6028,0.0031,0.0004</t>
+  </si>
+  <si>
+    <t>0.9216,0.0015,0.0641,0.0005</t>
+  </si>
+  <si>
+    <t>0.9147,0.0060,0.0426,0.0006</t>
+  </si>
+  <si>
+    <t>0.4557,0.0171,0.1392,0.0210</t>
+  </si>
+  <si>
+    <t>0.2481,0.0063,0.6717,0.0051</t>
+  </si>
+  <si>
+    <t>0.0003,0.3002,0.0005,0.9655</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9956,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.6667,0.3323,0.0040,0.0005</t>
+  </si>
+  <si>
+    <t>0.8758,0.1484,0.0016,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9961,0.0012,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.5317,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.4599,0.9965,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0265,0.9935,0.0001</t>
+  </si>
+  <si>
+    <t>0.0152,0.0027,0.9830,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0001,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.2751,0.0013,0.7194,0.0016</t>
+  </si>
+  <si>
+    <t>0.0902,0.0002,0.9358,0.0010</t>
+  </si>
+  <si>
+    <t>0.1530,0.0131,0.8213,0.0032</t>
+  </si>
+  <si>
+    <t>0.0023,0.0001,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.9978,0.0752,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0294,0.9677,0.0002,0.0033</t>
+  </si>
+  <si>
+    <t>0.2476,0.7951,0.0031,0.0015</t>
+  </si>
+  <si>
+    <t>0.0131,0.0001,0.0002,0.9956</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0220,0.9978,0.0008</t>
+  </si>
+  <si>
+    <t>0.9797,0.0001,0.0069,0.0026</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.1953,0.8627,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2137,0.7776,0.0032,0.0026</t>
+  </si>
+  <si>
+    <t>0.9920,0.0009,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0010,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.7982,0.1162,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.8577,0.1647,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.3555,0.7473,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0164,0.0521,0.9690,0.0024</t>
+  </si>
+  <si>
+    <t>0.9917,0.0089,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0013,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9977,0.0016,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9796,0.0164,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0023,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9557,0.0222,0.0095,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0097,0.9961,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0001,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.0126,0.9893,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0127,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0350,0.0013,0.9701,0.0007</t>
+  </si>
+  <si>
+    <t>0.0038,0.0010,0.9946,0.0003</t>
+  </si>
+  <si>
+    <t>0.9633,0.0019,0.0188,0.0005</t>
+  </si>
+  <si>
+    <t>0.1246,0.0089,0.7943,0.0004</t>
+  </si>
+  <si>
+    <t>0.0094,0.0230,0.9656,0.0004</t>
+  </si>
+  <si>
+    <t>0.8866,0.0415,0.0307,0.0014</t>
+  </si>
+  <si>
+    <t>0.1336,0.0134,0.7450,0.0053</t>
+  </si>
+  <si>
+    <t>0.1823,0.0094,0.8015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0258,0.9819,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0032,0.9962,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.1011,0.9385,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9158,0.0830,0.0011,0.0008</t>
+  </si>
+  <si>
+    <t>0.0272,0.9754,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9149,0.0301,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.8007,0.0011,0.1802,0.0015</t>
+  </si>
+  <si>
+    <t>0.9624,0.0032,0.0030,0.0079</t>
+  </si>
+  <si>
+    <t>0.9367,0.0220,0.0087,0.0018</t>
+  </si>
+  <si>
+    <t>0.9685,0.0033,0.0089,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0003,0.9970,0.0005</t>
+  </si>
+  <si>
+    <t>0.0488,0.0228,0.7774,0.0019</t>
+  </si>
+  <si>
+    <t>0.0014,0.0082,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0048,0.0010,0.9921,0.0001</t>
+  </si>
+  <si>
+    <t>0.0220,0.0126,0.9484,0.0036</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9975,0.0022,0.0003,0.0001</t>
   </si>
   <si>
     <t>0.9993,0.0005,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9724,0.0018,0.0143,0.0002</t>
-  </si>
-  <si>
-    <t>0.0033,0.0015,0.9941,0.0007</t>
-  </si>
-  <si>
-    <t>0.0088,0.0006,0.9930,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.9939,0.0002,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0060,0.9913,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9879,0.0009,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9107,0.0026,0.0532,0.0105</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9990,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.3056,0.7129,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.0591,0.0198,0.8766,0.0036</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0017</t>
-  </si>
-  <si>
-    <t>0.0021,0.9779,0.0855,0.0002</t>
-  </si>
-  <si>
-    <t>0.9836,0.0037,0.0023,0.0003</t>
-  </si>
-  <si>
-    <t>0.9439,0.0013,0.0319,0.0012</t>
-  </si>
-  <si>
-    <t>0.8158,0.2221,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.0004,0.9966,0.0298,0.0000</t>
-  </si>
-  <si>
-    <t>0.0247,0.4494,0.1866,0.0056</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.0008,0.9897,0.0002</t>
-  </si>
-  <si>
-    <t>0.0162,0.0000,0.9538,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.2957,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9974,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.7753,0.0021,0.9048</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.0146,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0045,0.0252,0.9860,0.0016</t>
-  </si>
-  <si>
-    <t>0.0014,0.0026,0.9958,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.0001,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9995,0.0002</t>
-  </si>
-  <si>
-    <t>0.0156,0.0010,0.9839,0.0004</t>
-  </si>
-  <si>
-    <t>0.9987,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0016,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0014,0.9996,0.0005</t>
-  </si>
-  <si>
-    <t>0.9970,0.0010,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9967,0.9649,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0055,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0004,0.9951,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9938,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9937,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9642,0.0004,0.0326,0.0001</t>
-  </si>
-  <si>
-    <t>0.8780,0.0017,0.0832,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9926,0.8701,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9116,0.4945,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9978,0.0105,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9932,0.8485,0.0000</t>
-  </si>
-  <si>
-    <t>0.0171,0.0000,0.0002,0.9960</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0002,1.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.8297,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.7216,0.9797,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.9385,0.6002,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.8270,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9718,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9290,0.9518,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0020,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9962,0.0044,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0006,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0007,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0014,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9938,0.0084,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
+    <t>0.9929,0.0060,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0023,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0033,0.0018,0.9961,0.0006</t>
+  </si>
+  <si>
+    <t>0.0086,0.0029,0.9884,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0002,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0376,0.9896,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0003,0.9986,0.0001</t>
   </si>
   <si>
     <t>0.0001,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0148,0.0016,0.9797,0.0018</t>
-  </si>
-  <si>
-    <t>0.9988,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9982,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.5394,0.4847,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.1272,0.0135,0.6592,0.0063</t>
-  </si>
-  <si>
-    <t>0.1564,0.0039,0.7548,0.0052</t>
-  </si>
-  <si>
-    <t>0.9757,0.0035,0.0037,0.0007</t>
-  </si>
-  <si>
-    <t>0.0265,0.0082,0.9610,0.0037</t>
-  </si>
-  <si>
-    <t>0.0005,0.0302,0.0008,0.9882</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9968,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.4533,0.4825,0.0150,0.0006</t>
-  </si>
-  <si>
-    <t>0.8456,0.1832,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0019,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0950,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0485,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0278,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.2510,0.0034,0.7675,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8811,0.0011,0.0614,0.0028</t>
-  </si>
-  <si>
-    <t>0.0033,0.0001,0.9969,0.0005</t>
-  </si>
-  <si>
-    <t>0.0779,0.0059,0.9320,0.0003</t>
-  </si>
-  <si>
-    <t>0.0054,0.0003,0.0005,0.9983</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0002,0.0001,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.9989,0.3055,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0050,0.9916,0.0001,0.0086</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0819,0.9098,0.0122,0.0040</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.5907,0.0001,0.0000,0.6386</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0034,0.9990,0.0016</t>
-  </si>
-  <si>
-    <t>0.9798,0.0001,0.0014,0.0096</t>
-  </si>
-  <si>
-    <t>0.9967,0.0011,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.0099,0.9864,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.1030,0.8999,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9819,0.0049,0.0030,0.0003</t>
-  </si>
-  <si>
-    <t>0.9959,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0004,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9379,0.0403,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.8565,0.1784,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.0664,0.9297,0.0021,0.0017</t>
-  </si>
-  <si>
-    <t>0.0064,0.1190,0.9830,0.0009</t>
-  </si>
-  <si>
-    <t>0.9509,0.0584,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.9966,0.0010,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9975,0.0021,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9806,0.0165,0.0015,0.0016</t>
-  </si>
-  <si>
-    <t>0.0000,0.0023,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9889,0.0068,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.0053,0.0140,0.9844,0.0030</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.0086,0.9925,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0019,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0013,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.0007,0.9954,0.0003</t>
-  </si>
-  <si>
-    <t>0.0150,0.0068,0.9759,0.0003</t>
-  </si>
-  <si>
-    <t>0.1337,0.0054,0.8195,0.0006</t>
-  </si>
-  <si>
-    <t>0.0039,0.0467,0.9683,0.0006</t>
-  </si>
-  <si>
-    <t>0.7353,0.0154,0.1971,0.0011</t>
-  </si>
-  <si>
-    <t>0.6236,0.0092,0.2660,0.0042</t>
-  </si>
-  <si>
-    <t>0.1186,0.0073,0.8756,0.0005</t>
-  </si>
-  <si>
-    <t>0.0034,0.9963,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9960,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.7704,0.3471,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.8794,0.1283,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.3308,0.7414,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.7835,0.1285,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0001,0.0056,0.0001</t>
-  </si>
-  <si>
-    <t>0.8656,0.0289,0.0085,0.0072</t>
-  </si>
-  <si>
-    <t>0.9519,0.0081,0.0124,0.0013</t>
-  </si>
-  <si>
-    <t>0.8639,0.0048,0.0965,0.0024</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0077,0.0013,0.9874,0.0009</t>
-  </si>
-  <si>
-    <t>0.0152,0.0155,0.9537,0.0025</t>
-  </si>
-  <si>
-    <t>0.0048,0.0010,0.9913,0.0006</t>
-  </si>
-  <si>
-    <t>0.0164,0.0132,0.9488,0.0055</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9960,0.0014,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9846,0.0135,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9929,0.0095,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9959,0.0038,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0014,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0012,0.9989,0.0010</t>
-  </si>
-  <si>
-    <t>0.0080,0.0109,0.9864,0.0004</t>
-  </si>
-  <si>
-    <t>0.9782,0.0005,0.0098,0.0010</t>
-  </si>
-  <si>
-    <t>0.0012,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0005,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.2689,0.9801,0.0004</t>
-  </si>
-  <si>
-    <t>0.0169,0.0003,0.9878,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0020,0.9983,0.0006</t>
-  </si>
-  <si>
-    <t>0.9755,0.0008,0.0099,0.0006</t>
-  </si>
-  <si>
-    <t>0.9885,0.0001,0.0073,0.0002</t>
-  </si>
-  <si>
-    <t>0.9960,0.0002,0.0009,0.0001</t>
+    <t>0.0006,0.0007,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.0012,0.0007,0.9971,0.0014</t>
+  </si>
+  <si>
+    <t>0.9438,0.0016,0.0255,0.0017</t>
+  </si>
+  <si>
+    <t>0.8927,0.0001,0.1780,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0008,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9963,0.0054,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0016,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0052,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0011,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9990,0.0006,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9929,0.0089,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9730,0.0411,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0033,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0014,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.0008,0.0011,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0169,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0025,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0069,0.9981,0.0005</t>
-  </si>
-  <si>
-    <t>0.0014,0.0015,0.9969,0.0006</t>
-  </si>
-  <si>
-    <t>0.0094,0.0007,0.9832,0.0117</t>
-  </si>
-  <si>
-    <t>0.0026,0.0010,0.9957,0.0003</t>
-  </si>
-  <si>
-    <t>0.0171,0.0000,0.9812,0.0003</t>
-  </si>
-  <si>
-    <t>0.9962,0.0001,0.0001,0.0024</t>
-  </si>
-  <si>
-    <t>0.0025,0.0004,0.0000,0.9993</t>
-  </si>
-  <si>
-    <t>0.0050,0.0000,0.0002,0.9983</t>
-  </si>
-  <si>
-    <t>0.9953,0.0002,0.0006,0.0009</t>
+    <t>0.9968,0.0014,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.0015,0.0012,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0358,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0050,0.9924,0.0010</t>
+  </si>
+  <si>
+    <t>0.0008,0.0505,0.9878,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.2429,0.0009,0.6762,0.0202</t>
+  </si>
+  <si>
+    <t>0.0033,0.0052,0.9906,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.0001,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0202,0.0001,0.0029,0.9881</t>
+  </si>
+  <si>
+    <t>0.9888,0.0007,0.0021,0.0015</t>
   </si>
 </sst>
 </file>
@@ -1893,7 +1896,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1907,7 +1910,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1921,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1935,7 +1938,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1949,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1963,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1977,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1991,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2005,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2019,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2033,7 +2036,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2047,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2061,7 +2064,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2075,7 +2078,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2089,7 +2092,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2103,7 +2106,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2117,7 +2120,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2131,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2145,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2159,7 +2162,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2173,7 +2176,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2201,7 +2204,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2212,10 +2215,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2229,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2243,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2257,7 +2260,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2271,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2285,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2299,7 +2302,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2310,10 +2313,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2327,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2341,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2355,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2369,7 +2372,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2383,7 +2386,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2397,7 +2400,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2408,10 +2411,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2425,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2439,7 +2442,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2450,10 +2453,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2467,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2481,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2495,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2506,10 +2509,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2523,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2537,7 +2540,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2551,7 +2554,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>283</v>
+        <v>311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2565,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2579,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2593,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2607,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2621,7 +2624,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2635,7 +2638,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2649,7 +2652,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2663,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2677,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2691,7 +2694,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2705,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2719,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2733,7 +2736,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2747,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2761,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2775,7 +2778,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2789,7 +2792,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2803,7 +2806,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2817,7 +2820,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2831,7 +2834,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2845,7 +2848,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2859,7 +2862,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2873,7 +2876,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2887,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2898,10 +2901,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2915,7 +2918,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2929,7 +2932,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2943,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2957,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2971,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2985,7 +2988,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2999,7 +3002,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3013,7 +3016,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3024,10 +3027,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3041,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3052,10 +3055,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3069,7 +3072,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3083,7 +3086,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3097,7 +3100,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3111,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3125,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3139,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3153,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3167,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3181,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3195,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3209,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3223,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3237,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3251,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>356</v>
+        <v>276</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3265,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3279,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3293,7 +3296,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3307,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3321,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3335,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3349,7 +3352,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3363,7 +3366,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3377,7 +3380,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3391,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3405,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3419,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3433,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3447,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3461,7 +3464,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3472,10 +3475,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3486,10 +3489,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3500,10 +3503,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3514,10 +3517,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3531,7 +3534,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3545,7 +3548,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3559,7 +3562,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3573,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3587,7 +3590,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3601,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3615,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3629,7 +3632,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3643,7 +3646,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3657,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3671,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>272</v>
+        <v>358</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3685,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3699,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3713,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3727,7 +3730,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3741,7 +3744,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3755,7 +3758,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3766,10 +3769,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3783,7 +3786,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3797,7 +3800,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3811,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3825,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3836,10 +3839,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3853,7 +3856,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3867,7 +3870,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3881,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3895,7 +3898,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3909,7 +3912,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>396</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3923,7 +3926,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3937,7 +3940,7 @@
         <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3951,7 +3954,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3965,7 +3968,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3979,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>401</v>
+        <v>352</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3993,7 +3996,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4007,7 +4010,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>358</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4021,7 +4024,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4035,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4049,7 +4052,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4063,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4077,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4091,7 +4094,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4105,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4119,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4133,7 +4136,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4147,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4161,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4175,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>415</v>
+        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4189,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>416</v>
+        <v>276</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4203,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4217,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>352</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4231,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4245,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4259,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>269</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4427,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>291</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4441,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4455,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4469,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4483,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4497,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>435</v>
+        <v>292</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4550,7 +4553,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
         <v>439</v>
@@ -4606,7 +4609,7 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
         <v>443</v>
@@ -4662,7 +4665,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>447</v>
@@ -4847,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>460</v>
+        <v>273</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4861,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4875,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4889,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4903,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>418</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -5043,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5071,7 +5074,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>435</v>
+        <v>474</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5085,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5099,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5113,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5127,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5141,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5155,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5169,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5183,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5197,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5211,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5225,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5239,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5253,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5267,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5281,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5295,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5309,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5323,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5337,7 +5340,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5351,7 +5354,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5365,7 +5368,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5379,7 +5382,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5393,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5407,7 +5410,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5421,7 +5424,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5435,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5449,7 +5452,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
